--- a/ACCY122/Session/S07/ACCY122 In Session L7 v1.0.xlsx
+++ b/ACCY122/Session/S07/ACCY122 In Session L7 v1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onlym\Desktop\Manek\Notes\SIM\UOW\2025 UOW\Learning Material\In Session Explanation\2025\L7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BBBA35-A71B-487F-9706-2E6B7C3EF80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9369A535-7810-4E18-881B-5572B320C663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18700" activeTab="4" xr2:uid="{BB81D00E-B7BD-4C7E-833A-F8ECA5DA9AD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{BB81D00E-B7BD-4C7E-833A-F8ECA5DA9AD9}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="7" r:id="rId1"/>
@@ -19,6 +19,10 @@
     <sheet name="Ex1" sheetId="10" r:id="rId4"/>
     <sheet name="LE" sheetId="12" r:id="rId5"/>
     <sheet name="Ex2" sheetId="11" r:id="rId6"/>
+    <sheet name="12.2 A" sheetId="13" r:id="rId7"/>
+    <sheet name="12.1 A" sheetId="16" r:id="rId8"/>
+    <sheet name="214 A" sheetId="14" r:id="rId9"/>
+    <sheet name="212 A" sheetId="15" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="221">
   <si>
     <t>Transactions</t>
   </si>
@@ -629,17 +633,164 @@
   <si>
     <t>Unadj bal</t>
   </si>
+  <si>
+    <t>Opening Allowance (1 July 2023) = 4464</t>
+  </si>
+  <si>
+    <t>Debtors after write-off (30 June 2024) = 97775</t>
+  </si>
+  <si>
+    <t>Bad debts written off = 3132</t>
+  </si>
+  <si>
+    <t>Required allowance = 3% of debtors</t>
+  </si>
+  <si>
+    <t>97,775 × 3% = 2,933.25 ≈ 2,933</t>
+  </si>
+  <si>
+    <t>Allowance for DD</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>allowance for DD is an contra asset account so dr - / cr +</t>
+  </si>
+  <si>
+    <t>balance</t>
+  </si>
+  <si>
+    <t>accounts receivable</t>
+  </si>
+  <si>
+    <t>bal c/d</t>
+  </si>
+  <si>
+    <t>bal b/d</t>
+  </si>
+  <si>
+    <t>bad debts expense</t>
+  </si>
+  <si>
+    <t>Customer officially defaulted</t>
+  </si>
+  <si>
+    <t>Dr Allowance for Doubtful Debts     3132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cr Accounts Receivable               3132</t>
+  </si>
+  <si>
+    <t>To increase allowance by 2933</t>
+  </si>
+  <si>
+    <t>Dr Bad Debt Expense          2933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cr Allowance for Doubtful Debts    2933</t>
+  </si>
+  <si>
+    <t>a)</t>
+  </si>
+  <si>
+    <t>b)</t>
+  </si>
+  <si>
+    <t>Clover Landscaping Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit and Loss Statement </t>
+  </si>
+  <si>
+    <t>for the year ended 30 jun 2024 (extract)</t>
+  </si>
+  <si>
+    <t>Expense</t>
+  </si>
+  <si>
+    <t>Bad debts</t>
+  </si>
+  <si>
+    <t>Statement for financial position</t>
+  </si>
+  <si>
+    <t>Current Assets</t>
+  </si>
+  <si>
+    <t>Account Receivable</t>
+  </si>
+  <si>
+    <t>LESS: Allowance for Doubtful debts</t>
+  </si>
+  <si>
+    <t>Total uncollectible = 34012</t>
+  </si>
+  <si>
+    <t>Amount to adjust = 34012 - 28947 = 5065</t>
+  </si>
+  <si>
+    <t>Dr Bad Debt Expense          5065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cr Allowance for Doubtful Debts    5065</t>
+  </si>
+  <si>
+    <t>c)</t>
+  </si>
+  <si>
+    <t>Dr Allowance for Doubtful Debts     3081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cr Accounts Receivable               3081</t>
+  </si>
+  <si>
+    <t>Estimated uncollectible accounts = ($52,000 × 1%) + ($8,000 × 15%) + ($3,200 × 40%) = $3,000</t>
+  </si>
+  <si>
+    <t>To adjust = $3,000 - $80 = $2920</t>
+  </si>
+  <si>
+    <t>Dr Bad Debt Expense          2920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cr Allowance for Doubtful Debts    2920</t>
+  </si>
+  <si>
+    <t>*Exercise 12.2 similar qn will be in exam</t>
+  </si>
+  <si>
+    <t>Total uncollectible = 35941</t>
+  </si>
+  <si>
+    <t>Amount to adjust = 35941 - 29397 = 6544</t>
+  </si>
+  <si>
+    <t>Dr Bad Debt Expense          6544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cr Allowance for Doubtful Debts    6544</t>
+  </si>
+  <si>
+    <t>Dr Allowance for Doubtful Debts     3231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cr Accounts Receivable               3231</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -676,6 +827,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -731,7 +890,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -902,12 +1061,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -946,39 +1116,47 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1025,8 +1203,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1023447" y="636641"/>
-          <a:ext cx="5361327" cy="5677194"/>
+          <a:off x="1026232" y="661707"/>
+          <a:ext cx="5386393" cy="5936207"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -1769,6 +1947,226 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>73781</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>171854</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39A3C6DA-D812-D1A9-2B81-BD29F7D55818}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="676275" y="323850"/>
+          <a:ext cx="6201640" cy="2896004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>211257</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>164758</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2FEA09E-CB05-42A6-EB58-901AD5D2B8E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="610914" y="190500"/>
+          <a:ext cx="6620799" cy="4553585"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>488133</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>95754</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61C86F9A-5DA3-0A7F-B2C5-2CC9D9B0F74E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647700" y="295275"/>
+          <a:ext cx="6392167" cy="3610479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>518949</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>142378</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>558363</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>10894</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B74B2BBA-158E-CCC0-2692-F4BB71845FAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1129863" y="142378"/>
+          <a:ext cx="5537638" cy="2535516"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Manek Mukesh" id="{EAD7B708-3F04-4908-A591-1BCBA73A0877}" userId="7baad15b6bef9919" providerId="Windows Live"/>
@@ -2085,8 +2483,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8D626B-C14C-46B5-8E1C-4CA9F7E39F10}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60AFD087-1C5D-44BA-B7CF-5CA64DEB1719}">
+  <dimension ref="B17:C23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C20" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2095,27 +2530,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3C8C239-724E-42F6-AF35-C0937B854444}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>9</v>
       </c>
@@ -2132,7 +2567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="11" t="s">
         <v>13</v>
       </c>
@@ -2150,7 +2585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="12" t="s">
@@ -2164,8 +2599,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C6" s="38" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="55" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="11"/>
@@ -2192,8 +2627,8 @@
       </c>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C7" s="38"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="55"/>
       <c r="D7" s="11"/>
       <c r="E7" s="12" t="s">
         <v>2</v>
@@ -2205,8 +2640,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C8" s="38"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="55"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
         <v>24</v>
@@ -2219,8 +2654,8 @@
       </c>
       <c r="O8" s="6"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C9" s="38"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C9" s="55"/>
       <c r="D9" s="11"/>
       <c r="E9" s="12" t="s">
         <v>2</v>
@@ -2228,8 +2663,8 @@
       <c r="M9" s="5"/>
       <c r="O9" s="6"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C10" s="38"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="55"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
         <v>26</v>
@@ -2257,7 +2692,7 @@
       </c>
       <c r="O10" s="6"/>
     </row>
-    <row r="11" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
@@ -2277,7 +2712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="12" t="s">
@@ -2294,7 +2729,7 @@
       </c>
       <c r="O12" s="6"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C13" s="11" t="s">
         <v>36</v>
       </c>
@@ -2311,7 +2746,7 @@
       <c r="M13" s="5"/>
       <c r="O13" s="6"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>38</v>
       </c>
@@ -2329,7 +2764,7 @@
       </c>
       <c r="O14" s="6"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M15" s="5" t="s">
         <v>40</v>
       </c>
@@ -2337,17 +2772,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M16" s="5" t="s">
         <v>41</v>
       </c>
       <c r="O16" s="6"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M17" s="5"/>
       <c r="O17" s="6"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K18">
         <v>4</v>
       </c>
@@ -2362,7 +2797,7 @@
       </c>
       <c r="O18" s="6"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M19" s="5" t="s">
         <v>44</v>
       </c>
@@ -2370,7 +2805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M20" s="7" t="s">
         <v>45</v>
       </c>
@@ -2391,12 +2826,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FABE87AE-180A-4385-BAD6-1291BDAAE5B8}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="11" width="18.08984375" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -2413,7 +2848,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>51</v>
       </c>
@@ -2424,7 +2859,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>54</v>
       </c>
@@ -2435,7 +2870,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>56</v>
       </c>
@@ -2458,7 +2893,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
@@ -2470,7 +2905,7 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -2493,7 +2928,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -2516,7 +2951,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>65</v>
       </c>
@@ -2537,7 +2972,7 @@
       <c r="J8" s="23"/>
       <c r="K8" s="24"/>
     </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -2549,7 +2984,7 @@
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>66</v>
       </c>
@@ -2572,7 +3007,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>67</v>
       </c>
@@ -2600,7 +3035,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="37"/>
       <c r="B12" s="37"/>
       <c r="C12" s="37"/>
@@ -2614,7 +3049,7 @@
       <c r="K12" s="37"/>
       <c r="L12" s="37"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>70</v>
       </c>
@@ -2638,7 +3073,7 @@
       </c>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>72</v>
       </c>
@@ -2664,7 +3099,7 @@
       </c>
       <c r="L14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="37"/>
       <c r="B15" s="37"/>
       <c r="C15" s="37"/>
@@ -2678,7 +3113,7 @@
       <c r="K15" s="37"/>
       <c r="L15" s="37"/>
     </row>
-    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>74</v>
       </c>
@@ -2704,7 +3139,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>76</v>
       </c>
@@ -2725,7 +3160,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>79</v>
       </c>
@@ -2743,7 +3178,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>82</v>
       </c>
@@ -2765,7 +3200,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="37"/>
       <c r="B20" s="37"/>
       <c r="C20" s="37"/>
@@ -2779,7 +3214,7 @@
       <c r="K20" s="37"/>
       <c r="L20" s="37"/>
     </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="37"/>
       <c r="B21" s="37"/>
       <c r="C21" s="37"/>
@@ -2793,7 +3228,7 @@
       <c r="K21" s="37"/>
       <c r="L21" s="37"/>
     </row>
-    <row r="22" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>83</v>
       </c>
@@ -2814,7 +3249,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>84</v>
       </c>
@@ -2829,7 +3264,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>86</v>
       </c>
@@ -2852,7 +3287,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="37"/>
       <c r="B25" s="37"/>
       <c r="C25" s="37"/>
@@ -2866,7 +3301,7 @@
       <c r="K25" s="37"/>
       <c r="L25" s="37"/>
     </row>
-    <row r="26" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>88</v>
       </c>
@@ -2887,7 +3322,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
@@ -2902,7 +3337,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:12" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" s="16" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>90</v>
       </c>
@@ -2925,11 +3360,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="33" s="16" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2938,20 +3373,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE15021-B040-458A-BE6C-8074E6921372}">
   <dimension ref="B2:M26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.54296875" customWidth="1"/>
-    <col min="2" max="2" width="40.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.5703125" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="21.81640625" customWidth="1"/>
-    <col min="5" max="5" width="30.7265625" customWidth="1"/>
-    <col min="6" max="6" width="8.36328125" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" customWidth="1"/>
-    <col min="8" max="8" width="7.6328125" customWidth="1"/>
-    <col min="9" max="9" width="7.453125" customWidth="1"/>
+    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" s="11" t="s">
         <v>92</v>
       </c>
@@ -2962,7 +3397,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>95</v>
       </c>
@@ -2970,7 +3405,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
         <v>97</v>
       </c>
@@ -2978,7 +3413,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>99</v>
       </c>
@@ -2992,7 +3427,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>102</v>
       </c>
@@ -3015,7 +3450,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>108</v>
       </c>
@@ -3035,7 +3470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G9">
         <v>200</v>
       </c>
@@ -3046,7 +3481,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="F10">
         <v>125</v>
       </c>
@@ -3054,7 +3489,7 @@
         <v>-125</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="E11" s="26" t="s">
         <v>113</v>
       </c>
@@ -3063,15 +3498,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="E12" s="26"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="E13" s="27" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="E14" t="s">
         <v>115</v>
       </c>
@@ -3079,12 +3514,12 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E15" s="27" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
       <c r="E16" s="28" t="s">
         <v>118</v>
       </c>
@@ -3105,7 +3540,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E17" t="s">
         <v>122</v>
       </c>
@@ -3131,7 +3566,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E18" t="s">
         <v>129</v>
       </c>
@@ -3146,7 +3581,7 @@
       </c>
       <c r="M18" s="6"/>
     </row>
-    <row r="19" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E19" t="s">
         <v>130</v>
       </c>
@@ -3163,7 +3598,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="20" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E20" t="s">
         <v>131</v>
       </c>
@@ -3178,15 +3613,15 @@
       </c>
       <c r="M20" s="6"/>
     </row>
-    <row r="21" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="5:13" x14ac:dyDescent="0.25">
       <c r="G21" s="30"/>
       <c r="M21" s="6"/>
     </row>
-    <row r="22" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="5:13" x14ac:dyDescent="0.25">
       <c r="G22" s="30"/>
       <c r="M22" s="6"/>
     </row>
-    <row r="23" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E23" t="s">
         <v>132</v>
       </c>
@@ -3200,7 +3635,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="5:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E24" t="s">
         <v>133</v>
       </c>
@@ -3233,7 +3668,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="25" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E25" t="s">
         <v>134</v>
       </c>
@@ -3256,7 +3691,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="26" spans="5:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="5:13" x14ac:dyDescent="0.25">
       <c r="E26" t="s">
         <v>135</v>
       </c>
@@ -3298,55 +3733,53 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089F55F2-E53C-44B8-B271-F795483F030A}">
   <dimension ref="A1:T16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.36328125" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7265625" customWidth="1"/>
-    <col min="14" max="14" width="5.08984375" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="5.140625" customWidth="1"/>
     <col min="15" max="15" width="8" customWidth="1"/>
-    <col min="16" max="16" width="14.1796875" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="51" t="s">
         <v>48</v>
       </c>
       <c r="J1" s="3"/>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="L1" s="54" t="s">
+      <c r="L1" s="51" t="s">
         <v>50</v>
       </c>
       <c r="M1" s="4"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>133</v>
       </c>
       <c r="F2" s="5"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48" t="s">
+      <c r="I2" t="s">
         <v>157</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" t="s">
         <v>54</v>
       </c>
-      <c r="K2" s="48" t="s">
+      <c r="K2" t="s">
         <v>106</v>
       </c>
-      <c r="L2" s="48" t="s">
+      <c r="L2" t="s">
         <v>107</v>
       </c>
       <c r="M2" s="6"/>
@@ -3359,159 +3792,136 @@
       <c r="S2" s="3"/>
       <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="38" t="s">
         <v>152</v>
       </c>
       <c r="F3" s="5"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48" t="s">
+      <c r="L3" t="s">
         <v>158</v>
       </c>
       <c r="M3" s="6"/>
       <c r="O3" s="5"/>
-      <c r="P3" s="48" t="s">
+      <c r="P3" t="s">
         <v>167</v>
       </c>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B4" s="39">
         <v>126500</v>
       </c>
       <c r="C4" s="32">
         <v>0.02</v>
       </c>
-      <c r="D4" s="40">
+      <c r="D4" s="39">
         <f>B4*C4</f>
         <v>2530</v>
       </c>
       <c r="F4" s="5"/>
-      <c r="G4" s="48" t="s">
+      <c r="G4" t="s">
         <v>161</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="48">
+      <c r="I4">
         <v>301100</v>
       </c>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
       <c r="M4" s="6"/>
       <c r="O4" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" t="s">
         <v>61</v>
       </c>
-      <c r="Q4" s="48" t="s">
+      <c r="Q4" t="s">
         <v>17</v>
       </c>
-      <c r="R4" s="48" t="s">
+      <c r="R4" t="s">
         <v>169</v>
       </c>
-      <c r="S4" s="48" t="s">
+      <c r="S4" t="s">
         <v>170</v>
       </c>
       <c r="T4" s="6"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="40">
+      <c r="B5" s="39">
         <v>89200</v>
       </c>
       <c r="C5" s="32">
         <v>0.12</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="39">
         <f t="shared" ref="D5:D7" si="0">B5*C5</f>
         <v>10704</v>
       </c>
       <c r="F5" s="5"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="55" t="s">
+      <c r="H5" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5">
         <v>-28947</v>
       </c>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="48"/>
       <c r="M5" s="6"/>
-      <c r="O5" s="49">
+      <c r="O5" s="47">
         <v>45869</v>
       </c>
-      <c r="P5" s="48" t="s">
+      <c r="P5" t="s">
         <v>171</v>
       </c>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="48"/>
-      <c r="S5" s="48">
+      <c r="S5">
         <v>28947</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="39">
         <v>53600</v>
       </c>
       <c r="C6" s="32">
         <v>0.18</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="39">
         <f t="shared" si="0"/>
         <v>9648</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
       <c r="M6" s="6"/>
-      <c r="O6" s="49">
+      <c r="O6" s="47">
         <v>45869</v>
       </c>
-      <c r="P6" s="48" t="s">
+      <c r="P6" t="s">
         <v>77</v>
       </c>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48">
+      <c r="R6">
         <v>5065</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="15">
         <f>S5-Q6+R6</f>
         <v>34012</v>
       </c>
@@ -3519,41 +3929,40 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="39">
         <v>31800</v>
       </c>
       <c r="C7" s="32">
         <v>0.35</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="39">
         <f t="shared" si="0"/>
         <v>11130</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="44">
+      <c r="H7" s="42"/>
+      <c r="I7" s="43">
         <f>D9*-1</f>
         <v>-5065</v>
       </c>
-      <c r="J7" s="43" t="s">
+      <c r="J7" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="43"/>
-      <c r="L7" s="45">
+      <c r="K7" s="42"/>
+      <c r="L7" s="44">
         <f>I7</f>
         <v>-5065</v>
       </c>
-      <c r="M7" s="46" t="s">
+      <c r="M7" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="O7" s="51">
+      <c r="O7" s="48">
         <v>45884</v>
       </c>
       <c r="P7" s="8" t="s">
@@ -3564,7 +3973,7 @@
         <v>3081</v>
       </c>
       <c r="R7" s="8"/>
-      <c r="S7" s="52">
+      <c r="S7" s="49">
         <f>S6-Q7+R7</f>
         <v>30931</v>
       </c>
@@ -3572,15 +3981,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>133</v>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="39">
         <f>SUM(B4:B7)</f>
         <v>301100</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="46">
         <f>SUM(D4:D7)</f>
         <v>34012</v>
       </c>
@@ -3588,16 +3997,10 @@
         <v>154</v>
       </c>
       <c r="F8" s="5"/>
-      <c r="G8" s="48"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
       <c r="M8" s="6"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D9" s="41">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D9" s="40">
         <f>D8-D10</f>
         <v>5065</v>
       </c>
@@ -3605,118 +4008,88 @@
         <v>156</v>
       </c>
       <c r="F9" s="5"/>
-      <c r="G9" s="48" t="s">
+      <c r="G9" t="s">
         <v>164</v>
       </c>
-      <c r="H9" s="48" t="s">
+      <c r="H9" t="s">
         <v>159</v>
       </c>
-      <c r="I9" s="48">
+      <c r="I9">
         <f>I4</f>
         <v>301100</v>
       </c>
-      <c r="J9" s="48"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
       <c r="M9" s="6"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="D10" s="40">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="D10" s="39">
         <v>28947</v>
       </c>
       <c r="E10" t="s">
         <v>155</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="55" t="s">
+      <c r="H10" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="I10" s="56">
+      <c r="I10" s="52">
         <f>D8*-1</f>
         <v>-34012</v>
       </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="48"/>
       <c r="M10" s="6"/>
     </row>
-    <row r="11" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F11" s="5"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="48"/>
       <c r="M11" s="6"/>
     </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="F12" s="42" t="s">
+    <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="G12" s="57">
+      <c r="G12" s="33">
         <v>45884</v>
       </c>
-      <c r="H12" s="48" t="s">
+      <c r="H12" t="s">
         <v>57</v>
       </c>
-      <c r="I12" s="58">
+      <c r="I12" s="53">
         <v>-3081</v>
       </c>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
       <c r="M12" s="6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F13" s="5"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="48" t="s">
+      <c r="H13" t="s">
         <v>160</v>
       </c>
-      <c r="I13" s="59">
+      <c r="I13" s="11">
         <v>3081</v>
       </c>
-      <c r="J13" s="48"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="48"/>
       <c r="M13" s="6"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F14" s="5"/>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="48"/>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48"/>
-      <c r="L14" s="48"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="F15" s="5"/>
-      <c r="G15" s="48" t="s">
+      <c r="G15" t="s">
         <v>163</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48">
+      <c r="I15">
         <f>I9+I12</f>
         <v>298019</v>
       </c>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F16" s="7"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="I16" s="60">
+      <c r="I16" s="54">
         <f>I10+I13</f>
         <v>-30931</v>
       </c>
@@ -3734,13 +4107,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15D3159-7B4D-48B5-9560-8DAC2F67DAC8}">
   <dimension ref="A2:I18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="38.453125" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>136</v>
       </c>
@@ -3751,7 +4124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="33">
         <v>44926</v>
       </c>
@@ -3768,7 +4141,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>140</v>
       </c>
@@ -3783,12 +4156,12 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>44926</v>
       </c>
@@ -3796,7 +4169,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>118</v>
       </c>
@@ -3814,7 +4187,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>146</v>
       </c>
@@ -3837,7 +4210,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>129</v>
       </c>
@@ -3852,7 +4225,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>130</v>
       </c>
@@ -3869,7 +4242,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>131</v>
       </c>
@@ -3884,15 +4257,15 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C13" s="30"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C14" s="30"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>132</v>
       </c>
@@ -3906,7 +4279,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>133</v>
       </c>
@@ -3939,7 +4312,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>134</v>
       </c>
@@ -3962,7 +4335,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>135</v>
       </c>
@@ -3998,4 +4371,679 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065DF0C6-4729-4CDB-86A6-877DD944AB3C}">
+  <dimension ref="B1:M48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="19.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B1" s="61" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J5" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="M5" s="26"/>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J6" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="M6" s="26"/>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J7" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="M7" s="26"/>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="J8" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="M8" s="26"/>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>176</v>
+      </c>
+      <c r="L21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C22" s="60" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" t="s">
+        <v>178</v>
+      </c>
+      <c r="D23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <v>2024</v>
+      </c>
+      <c r="F24">
+        <v>2023</v>
+      </c>
+      <c r="L24" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C25" s="56">
+        <v>46203</v>
+      </c>
+      <c r="D25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25">
+        <v>3132</v>
+      </c>
+      <c r="F25" s="33">
+        <v>46204</v>
+      </c>
+      <c r="G25" t="s">
+        <v>181</v>
+      </c>
+      <c r="H25">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <v>2024</v>
+      </c>
+      <c r="L26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C27" s="33">
+        <v>46203</v>
+      </c>
+      <c r="D27" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27">
+        <v>4265</v>
+      </c>
+      <c r="F27" s="33">
+        <v>46203</v>
+      </c>
+      <c r="G27" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E28" s="57">
+        <v>7397</v>
+      </c>
+      <c r="H28" s="57">
+        <v>7397</v>
+      </c>
+      <c r="L28" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <v>2025</v>
+      </c>
+      <c r="L29" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="F30" s="33">
+        <v>46204</v>
+      </c>
+      <c r="G30" t="s">
+        <v>184</v>
+      </c>
+      <c r="H30">
+        <v>4265</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C33" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C34" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C35" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C37" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C38" s="59" t="s">
+        <v>198</v>
+      </c>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C41" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C42" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C43" s="58" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" s="58"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C45" s="59" t="s">
+        <v>200</v>
+      </c>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C46" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46">
+        <v>97775</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C47" t="s">
+        <v>202</v>
+      </c>
+      <c r="H47">
+        <v>4265</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H48" s="57">
+        <v>93510</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C36:G36"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79E39D77-A56C-4B65-95A0-99CD710C6F6F}">
+  <dimension ref="B9:M44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K9">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="10" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K10">
+        <v>9070</v>
+      </c>
+    </row>
+    <row r="11" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K11">
+        <v>8816</v>
+      </c>
+    </row>
+    <row r="12" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="K12">
+        <v>11655</v>
+      </c>
+      <c r="M12" s="62"/>
+    </row>
+    <row r="13" spans="11:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="57">
+        <f>SUM(K9:K12)</f>
+        <v>35941</v>
+      </c>
+      <c r="M13" s="62"/>
+    </row>
+    <row r="14" spans="11:13" x14ac:dyDescent="0.25">
+      <c r="M14" s="62"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C31" s="33">
+        <v>46234</v>
+      </c>
+      <c r="D31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="33">
+        <v>46249</v>
+      </c>
+      <c r="D34" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="60" t="s">
+        <v>177</v>
+      </c>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="60"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>178</v>
+      </c>
+      <c r="D39" t="s">
+        <v>179</v>
+      </c>
+      <c r="E39" t="s">
+        <v>3</v>
+      </c>
+      <c r="F39" t="s">
+        <v>178</v>
+      </c>
+      <c r="G39" t="s">
+        <v>179</v>
+      </c>
+      <c r="H39" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <v>2019</v>
+      </c>
+      <c r="F40">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C41" s="56">
+        <v>46249</v>
+      </c>
+      <c r="D41" t="s">
+        <v>182</v>
+      </c>
+      <c r="E41">
+        <v>3231</v>
+      </c>
+      <c r="F41" s="33">
+        <v>46234</v>
+      </c>
+      <c r="G41" t="s">
+        <v>181</v>
+      </c>
+      <c r="H41">
+        <v>29397</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F42" s="33">
+        <v>46234</v>
+      </c>
+      <c r="G42" t="s">
+        <v>185</v>
+      </c>
+      <c r="H42">
+        <v>6544</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C43" s="56">
+        <v>46249</v>
+      </c>
+      <c r="D43" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43">
+        <v>32710</v>
+      </c>
+      <c r="F43" s="33"/>
+    </row>
+    <row r="44" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E44" s="57">
+        <v>35941</v>
+      </c>
+      <c r="H44" s="57">
+        <v>35941</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C38:H38"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9629050-310E-42A8-B201-0F3D32AF2DD6}">
+  <dimension ref="B24:H42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="33">
+        <v>46234</v>
+      </c>
+      <c r="D27" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>193</v>
+      </c>
+      <c r="C30" s="33">
+        <v>46249</v>
+      </c>
+      <c r="D30" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="60" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
+        <v>178</v>
+      </c>
+      <c r="D35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" t="s">
+        <v>178</v>
+      </c>
+      <c r="G35" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C36">
+        <v>2019</v>
+      </c>
+      <c r="F36">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C37" s="56">
+        <v>46249</v>
+      </c>
+      <c r="D37" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37">
+        <v>3081</v>
+      </c>
+      <c r="F37" s="33">
+        <v>46234</v>
+      </c>
+      <c r="G37" t="s">
+        <v>181</v>
+      </c>
+      <c r="H37">
+        <v>28947</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F38" s="33">
+        <v>46234</v>
+      </c>
+      <c r="G38" t="s">
+        <v>185</v>
+      </c>
+      <c r="H38">
+        <v>5065</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="C39" s="56">
+        <v>46249</v>
+      </c>
+      <c r="D39" t="s">
+        <v>183</v>
+      </c>
+      <c r="E39">
+        <v>30931</v>
+      </c>
+      <c r="F39" s="33"/>
+    </row>
+    <row r="40" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E40" s="57">
+        <v>34012</v>
+      </c>
+      <c r="H40" s="57">
+        <v>34012</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="F42" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C34:H34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>